--- a/Test Cases Execution.xlsx
+++ b/Test Cases Execution.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Opencart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84580417-7348-4F2D-AF6A-FEE3C5938106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6906C9-8AFD-4C70-9BAC-8C67D6BDDE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -15765,7 +15765,9 @@
       <c r="D2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15"/>
+      <c r="E2" s="15">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18.75">
       <c r="A3" s="16" t="s">
@@ -15780,7 +15782,9 @@
       <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="18"/>
+      <c r="E3" s="18">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="18.75">
       <c r="A4" s="13" t="s">
@@ -15795,7 +15799,9 @@
       <c r="D4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="18.75">
       <c r="A5" s="16" t="s">
@@ -15810,7 +15816,9 @@
       <c r="D5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="18">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="13" t="s">
@@ -15825,7 +15833,9 @@
       <c r="D6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="15">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18.75">
       <c r="A7" s="16" t="s">
@@ -15840,7 +15850,9 @@
       <c r="D7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="18">
+        <v>24</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18.75">
       <c r="A8" s="13" t="s">
@@ -15855,7 +15867,9 @@
       <c r="D8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="15"/>
+      <c r="E8" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="18.75">
       <c r="A9" s="16" t="s">
@@ -15870,7 +15884,9 @@
       <c r="D9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="18">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18.75">
       <c r="A10" s="13" t="s">
@@ -15885,7 +15901,9 @@
       <c r="D10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="15">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="18.75">
       <c r="A11" s="16" t="s">
@@ -15900,7 +15918,9 @@
       <c r="D11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="18"/>
+      <c r="E11" s="18">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="18.75">
       <c r="A12" s="13" t="s">
@@ -15915,7 +15935,9 @@
       <c r="D12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="18.75">
       <c r="A13" s="16" t="s">
@@ -15930,7 +15952,9 @@
       <c r="D13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="18"/>
+      <c r="E13" s="18">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="18.75">
       <c r="A14" s="13" t="s">
@@ -15945,7 +15969,9 @@
       <c r="D14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="15"/>
+      <c r="E14" s="15">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="18.75">
       <c r="A15" s="16" t="s">
@@ -15960,7 +15986,9 @@
       <c r="D15" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="18">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="18.75">
       <c r="A16" s="13" t="s">
@@ -15975,7 +16003,9 @@
       <c r="D16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="15">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="18.75">
       <c r="A17" s="16" t="s">
@@ -15990,7 +16020,9 @@
       <c r="D17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="18">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="18.75">
       <c r="A18" s="13" t="s">
@@ -16005,7 +16037,9 @@
       <c r="D18" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="15"/>
+      <c r="E18" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="18.75">
       <c r="A19" s="16" t="s">
@@ -16020,7 +16054,9 @@
       <c r="D19" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="18">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="18.75">
       <c r="A20" s="13" t="s">
@@ -16035,7 +16071,9 @@
       <c r="D20" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="15"/>
+      <c r="E20" s="15">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="18.75">
       <c r="A21" s="16" t="s">
@@ -16050,7 +16088,9 @@
       <c r="D21" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="18"/>
+      <c r="E21" s="18">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="18.75">
       <c r="A22" s="13" t="s">
@@ -16065,7 +16105,9 @@
       <c r="D22" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="15"/>
+      <c r="E22" s="15">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="18.75">
       <c r="A23" s="13" t="s">
@@ -16080,7 +16122,9 @@
       <c r="D23" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="15"/>
+      <c r="E23" s="15">
+        <v>14</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="18.75">
       <c r="A24" s="16" t="s">
@@ -16095,7 +16139,9 @@
       <c r="D24" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="18">
+        <v>13</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="18.75">
       <c r="A25" s="16" t="s">
@@ -16110,7 +16156,9 @@
       <c r="D25" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="18"/>
+      <c r="E25" s="18">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="18.75">
       <c r="A26" s="13" t="s">
@@ -16125,7 +16173,9 @@
       <c r="D26" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="15"/>
+      <c r="E26" s="15">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
